--- a/Experiments/outputs/scenario_6_np.xlsx
+++ b/Experiments/outputs/scenario_6_np.xlsx
@@ -530,55 +530,55 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>247.9454895822545</v>
+        <v>281.2461850323757</v>
       </c>
       <c r="D2" t="n">
-        <v>0.05336713790893555</v>
+        <v>0.1494629383087158</v>
       </c>
       <c r="E2" t="n">
-        <v>58</v>
+        <v>72</v>
       </c>
       <c r="F2" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H2" t="n">
-        <v>441.6650436877514</v>
+        <v>400.7763855545284</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1488471031188965</v>
+        <v>0.8795740604400635</v>
       </c>
       <c r="J2" t="n">
-        <v>76</v>
+        <v>104</v>
       </c>
       <c r="K2" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="L2" t="n">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="M2" t="n">
-        <v>1305.91715911446</v>
+        <v>1217.953476235902</v>
       </c>
       <c r="N2" t="n">
-        <v>1.463536024093628</v>
+        <v>1.723850727081299</v>
       </c>
       <c r="O2" t="n">
-        <v>380</v>
+        <v>570</v>
       </c>
       <c r="P2" t="n">
         <v>2</v>
       </c>
       <c r="Q2" t="n">
-        <v>1072</v>
+        <v>1457</v>
       </c>
       <c r="R2" t="n">
-        <v>0.8101368927946501</v>
+        <v>0.7690829818052082</v>
       </c>
       <c r="S2" t="n">
-        <v>0.6617970438590118</v>
+        <v>0.6709427795278913</v>
       </c>
     </row>
     <row r="3">
@@ -591,55 +591,55 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>206.834645882476</v>
+        <v>239.9122100994783</v>
       </c>
       <c r="D3" t="n">
-        <v>0.05863499641418457</v>
+        <v>0.1136729717254639</v>
       </c>
       <c r="E3" t="n">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="F3" t="n">
+        <v>13</v>
+      </c>
+      <c r="G3" t="n">
+        <v>7</v>
+      </c>
+      <c r="H3" t="n">
+        <v>374.2023931761979</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.7135188579559326</v>
+      </c>
+      <c r="J3" t="n">
+        <v>90</v>
+      </c>
+      <c r="K3" t="n">
         <v>12</v>
       </c>
-      <c r="G3" t="n">
-        <v>6</v>
-      </c>
-      <c r="H3" t="n">
-        <v>513.1926520148467</v>
-      </c>
-      <c r="I3" t="n">
-        <v>0.1611542701721191</v>
-      </c>
-      <c r="J3" t="n">
-        <v>70</v>
-      </c>
-      <c r="K3" t="n">
-        <v>24</v>
-      </c>
       <c r="L3" t="n">
-        <v>93</v>
+        <v>79</v>
       </c>
       <c r="M3" t="n">
-        <v>1334.245789499943</v>
+        <v>1211.583282193308</v>
       </c>
       <c r="N3" t="n">
-        <v>1.524989128112793</v>
+        <v>1.481994152069092</v>
       </c>
       <c r="O3" t="n">
-        <v>394</v>
+        <v>568</v>
       </c>
       <c r="P3" t="n">
         <v>1</v>
       </c>
       <c r="Q3" t="n">
-        <v>1031</v>
+        <v>1460</v>
       </c>
       <c r="R3" t="n">
-        <v>0.8449801022343906</v>
+        <v>0.8019845489571552</v>
       </c>
       <c r="S3" t="n">
-        <v>0.6153687303692491</v>
+        <v>0.6911459586180608</v>
       </c>
     </row>
     <row r="4">
@@ -652,55 +652,55 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>235.6408788447881</v>
+        <v>227.9326281110552</v>
       </c>
       <c r="D4" t="n">
-        <v>0.06479811668395996</v>
+        <v>0.1564571857452393</v>
       </c>
       <c r="E4" t="n">
-        <v>64</v>
+        <v>96</v>
       </c>
       <c r="F4" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="G4" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="H4" t="n">
-        <v>447.8141987141977</v>
+        <v>405.1927854180741</v>
       </c>
       <c r="I4" t="n">
-        <v>0.177523136138916</v>
+        <v>0.6061549186706543</v>
       </c>
       <c r="J4" t="n">
-        <v>70</v>
+        <v>101</v>
       </c>
       <c r="K4" t="n">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="L4" t="n">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="M4" t="n">
-        <v>1290.544545198799</v>
+        <v>1269.19835304128</v>
       </c>
       <c r="N4" t="n">
-        <v>1.455065011978149</v>
+        <v>2.500491142272949</v>
       </c>
       <c r="O4" t="n">
-        <v>373</v>
+        <v>582</v>
       </c>
       <c r="P4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>991</v>
+        <v>1480</v>
       </c>
       <c r="R4" t="n">
-        <v>0.8174097285355698</v>
+        <v>0.8204121305666067</v>
       </c>
       <c r="S4" t="n">
-        <v>0.6530036871798056</v>
+        <v>0.6807490456892396</v>
       </c>
     </row>
     <row r="5">
@@ -713,55 +713,55 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>205.1579667394439</v>
+        <v>249.3166740187788</v>
       </c>
       <c r="D5" t="n">
-        <v>0.05512094497680664</v>
+        <v>0.2247951030731201</v>
       </c>
       <c r="E5" t="n">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="F5" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="G5" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="H5" t="n">
-        <v>406.4499338559386</v>
+        <v>350.8408133846655</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1448209285736084</v>
+        <v>0.7240190505981445</v>
       </c>
       <c r="J5" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="K5" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="L5" t="n">
-        <v>88</v>
+        <v>70</v>
       </c>
       <c r="M5" t="n">
-        <v>1307.45743653207</v>
+        <v>1218.818676636971</v>
       </c>
       <c r="N5" t="n">
-        <v>1.482603073120117</v>
+        <v>2.308871984481812</v>
       </c>
       <c r="O5" t="n">
-        <v>364</v>
+        <v>551</v>
       </c>
       <c r="P5" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="Q5" t="n">
-        <v>1031</v>
+        <v>1390</v>
       </c>
       <c r="R5" t="n">
-        <v>0.8430863131700794</v>
+        <v>0.7954439993431127</v>
       </c>
       <c r="S5" t="n">
-        <v>0.6891295100710768</v>
+        <v>0.7121468352021615</v>
       </c>
     </row>
     <row r="6">
@@ -774,55 +774,55 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>208.5878385622051</v>
+        <v>219.0776061269588</v>
       </c>
       <c r="D6" t="n">
-        <v>0.05730509757995605</v>
+        <v>0.130742073059082</v>
       </c>
       <c r="E6" t="n">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F6" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H6" t="n">
-        <v>387.9626898110853</v>
+        <v>387.9169785204478</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1598660945892334</v>
+        <v>0.7159438133239746</v>
       </c>
       <c r="J6" t="n">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="K6" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="L6" t="n">
-        <v>92</v>
+        <v>75</v>
       </c>
       <c r="M6" t="n">
-        <v>1297.09310068116</v>
+        <v>1239.874814558726</v>
       </c>
       <c r="N6" t="n">
-        <v>1.426419973373413</v>
+        <v>1.474080085754395</v>
       </c>
       <c r="O6" t="n">
-        <v>404</v>
+        <v>563</v>
       </c>
       <c r="P6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Q6" t="n">
-        <v>1056</v>
+        <v>1417</v>
       </c>
       <c r="R6" t="n">
-        <v>0.8391882290849698</v>
+        <v>0.8233066729362278</v>
       </c>
       <c r="S6" t="n">
-        <v>0.7008983475377757</v>
+        <v>0.6871321411117555</v>
       </c>
     </row>
     <row r="7">
@@ -835,55 +835,55 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>242.0189594732665</v>
+        <v>227.5932535071155</v>
       </c>
       <c r="D7" t="n">
-        <v>0.05986690521240234</v>
+        <v>0.1005399227142334</v>
       </c>
       <c r="E7" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="F7" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="G7" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="H7" t="n">
-        <v>412.0466474509082</v>
+        <v>365.8332612446242</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1422600746154785</v>
+        <v>0.4925880432128906</v>
       </c>
       <c r="J7" t="n">
-        <v>60</v>
+        <v>77</v>
       </c>
       <c r="K7" t="n">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="L7" t="n">
-        <v>87</v>
+        <v>72</v>
       </c>
       <c r="M7" t="n">
-        <v>1256.442916301324</v>
+        <v>1211.118413059447</v>
       </c>
       <c r="N7" t="n">
-        <v>1.307800769805908</v>
+        <v>1.626605033874512</v>
       </c>
       <c r="O7" t="n">
-        <v>375</v>
+        <v>552</v>
       </c>
       <c r="P7" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="Q7" t="n">
-        <v>1007</v>
+        <v>1393</v>
       </c>
       <c r="R7" t="n">
-        <v>0.8073776720507811</v>
+        <v>0.8120800979879543</v>
       </c>
       <c r="S7" t="n">
-        <v>0.6720530299427546</v>
+        <v>0.6979376605129134</v>
       </c>
     </row>
     <row r="8">
@@ -896,55 +896,55 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>272.6424864594995</v>
+        <v>235.0894615266422</v>
       </c>
       <c r="D8" t="n">
-        <v>0.05061483383178711</v>
+        <v>0.1430320739746094</v>
       </c>
       <c r="E8" t="n">
-        <v>54</v>
+        <v>77</v>
       </c>
       <c r="F8" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="G8" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="H8" t="n">
-        <v>442.7267739892468</v>
+        <v>392.3461679489122</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1616709232330322</v>
+        <v>0.7079448699951172</v>
       </c>
       <c r="J8" t="n">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="K8" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="L8" t="n">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="M8" t="n">
-        <v>1291.15384234338</v>
+        <v>1190.290510666313</v>
       </c>
       <c r="N8" t="n">
-        <v>1.570627212524414</v>
+        <v>1.627985239028931</v>
       </c>
       <c r="O8" t="n">
-        <v>397</v>
+        <v>571</v>
       </c>
       <c r="P8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q8" t="n">
-        <v>1055</v>
+        <v>1489</v>
       </c>
       <c r="R8" t="n">
-        <v>0.7888381093575442</v>
+        <v>0.8024940471086831</v>
       </c>
       <c r="S8" t="n">
-        <v>0.6571076509475279</v>
+        <v>0.6703778074066299</v>
       </c>
     </row>
     <row r="9">
@@ -957,55 +957,55 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>226.6842753091106</v>
+        <v>301.5847821369284</v>
       </c>
       <c r="D9" t="n">
-        <v>0.06703901290893555</v>
+        <v>0.08986496925354004</v>
       </c>
       <c r="E9" t="n">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="F9" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G9" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H9" t="n">
-        <v>495.4696666458786</v>
+        <v>437.2475596639467</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1884410381317139</v>
+        <v>0.471444845199585</v>
       </c>
       <c r="J9" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="K9" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="L9" t="n">
-        <v>95</v>
+        <v>81</v>
       </c>
       <c r="M9" t="n">
-        <v>1363.971658158541</v>
+        <v>1206.510081271314</v>
       </c>
       <c r="N9" t="n">
-        <v>1.613556146621704</v>
+        <v>1.435776948928833</v>
       </c>
       <c r="O9" t="n">
-        <v>391</v>
+        <v>550</v>
       </c>
       <c r="P9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Q9" t="n">
-        <v>999</v>
+        <v>1376</v>
       </c>
       <c r="R9" t="n">
-        <v>0.8338057290610054</v>
+        <v>0.7500354229786917</v>
       </c>
       <c r="S9" t="n">
-        <v>0.6367448959204931</v>
+        <v>0.63759311550616</v>
       </c>
     </row>
     <row r="10">
@@ -1018,55 +1018,55 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>321.3648853228096</v>
+        <v>243.2215944210758</v>
       </c>
       <c r="D10" t="n">
-        <v>0.0536801815032959</v>
+        <v>0.0989837646484375</v>
       </c>
       <c r="E10" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="F10" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H10" t="n">
-        <v>429.770346130981</v>
+        <v>354.0756188751545</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1599991321563721</v>
+        <v>0.4266581535339355</v>
       </c>
       <c r="J10" t="n">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="K10" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="L10" t="n">
-        <v>97</v>
+        <v>77</v>
       </c>
       <c r="M10" t="n">
-        <v>1317.942980650182</v>
+        <v>1200.317252164006</v>
       </c>
       <c r="N10" t="n">
-        <v>1.571987152099609</v>
+        <v>1.453824996948242</v>
       </c>
       <c r="O10" t="n">
-        <v>400</v>
+        <v>526</v>
       </c>
       <c r="P10" t="n">
         <v>1</v>
       </c>
       <c r="Q10" t="n">
-        <v>1095</v>
+        <v>1283</v>
       </c>
       <c r="R10" t="n">
-        <v>0.7561617687251763</v>
+        <v>0.7973689089425475</v>
       </c>
       <c r="S10" t="n">
-        <v>0.67390824000674</v>
+        <v>0.7050149714695801</v>
       </c>
     </row>
     <row r="11">
@@ -1079,55 +1079,55 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>242.4511232199717</v>
+        <v>236.2186162179478</v>
       </c>
       <c r="D11" t="n">
-        <v>0.05635714530944824</v>
+        <v>0.1264550685882568</v>
       </c>
       <c r="E11" t="n">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="F11" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="G11" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="H11" t="n">
-        <v>403.5774343121496</v>
+        <v>425.4456313357451</v>
       </c>
       <c r="I11" t="n">
-        <v>0.1579458713531494</v>
+        <v>0.5759949684143066</v>
       </c>
       <c r="J11" t="n">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="K11" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="L11" t="n">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="M11" t="n">
-        <v>1331.990001261</v>
+        <v>1197.884626888529</v>
       </c>
       <c r="N11" t="n">
-        <v>1.437018156051636</v>
+        <v>1.732196092605591</v>
       </c>
       <c r="O11" t="n">
-        <v>389</v>
+        <v>548</v>
       </c>
       <c r="P11" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>1024</v>
+        <v>1404</v>
       </c>
       <c r="R11" t="n">
-        <v>0.8179782708650649</v>
+        <v>0.8028035330651844</v>
       </c>
       <c r="S11" t="n">
-        <v>0.6970116638037214</v>
+        <v>0.6448358867073637</v>
       </c>
     </row>
     <row r="12">
@@ -1140,10 +1140,10 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>211.2426993864082</v>
+        <v>211.1614560013097</v>
       </c>
       <c r="D12" t="n">
-        <v>0.06235814094543457</v>
+        <v>0.1356360912322998</v>
       </c>
       <c r="E12" t="n">
         <v>74</v>
@@ -1152,43 +1152,43 @@
         <v>10</v>
       </c>
       <c r="G12" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="H12" t="n">
-        <v>487.5175560064131</v>
+        <v>365.5923965588206</v>
       </c>
       <c r="I12" t="n">
-        <v>0.1866717338562012</v>
+        <v>0.7028031349182129</v>
       </c>
       <c r="J12" t="n">
         <v>87</v>
       </c>
       <c r="K12" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="L12" t="n">
-        <v>102</v>
+        <v>84</v>
       </c>
       <c r="M12" t="n">
-        <v>1314.775706659074</v>
+        <v>1236.403427951928</v>
       </c>
       <c r="N12" t="n">
-        <v>1.875214099884033</v>
+        <v>1.515961885452271</v>
       </c>
       <c r="O12" t="n">
-        <v>379</v>
+        <v>578</v>
       </c>
       <c r="P12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>976</v>
+        <v>1479</v>
       </c>
       <c r="R12" t="n">
-        <v>0.8393317595415657</v>
+        <v>0.8292131425491973</v>
       </c>
       <c r="S12" t="n">
-        <v>0.62920097052506</v>
+        <v>0.7043097840933557</v>
       </c>
     </row>
     <row r="13">
@@ -1201,55 +1201,55 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>321.4230430746122</v>
+        <v>244.798452875644</v>
       </c>
       <c r="D13" t="n">
-        <v>0.0464472770690918</v>
+        <v>0.09227085113525391</v>
       </c>
       <c r="E13" t="n">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="F13" t="n">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="G13" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H13" t="n">
-        <v>538.1333037901327</v>
+        <v>379.5192123276357</v>
       </c>
       <c r="I13" t="n">
-        <v>0.1615111827850342</v>
+        <v>0.5198299884796143</v>
       </c>
       <c r="J13" t="n">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="K13" t="n">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="L13" t="n">
-        <v>99</v>
+        <v>80</v>
       </c>
       <c r="M13" t="n">
-        <v>1380.336877335659</v>
+        <v>1227.034194508545</v>
       </c>
       <c r="N13" t="n">
-        <v>1.734287023544312</v>
+        <v>1.389037132263184</v>
       </c>
       <c r="O13" t="n">
-        <v>391</v>
+        <v>563</v>
       </c>
       <c r="P13" t="n">
         <v>1</v>
       </c>
       <c r="Q13" t="n">
-        <v>1075</v>
+        <v>1424</v>
       </c>
       <c r="R13" t="n">
-        <v>0.7671415953944326</v>
+        <v>0.8004958183144266</v>
       </c>
       <c r="S13" t="n">
-        <v>0.6101435000209199</v>
+        <v>0.6907020081215898</v>
       </c>
     </row>
     <row r="14">
@@ -1262,55 +1262,55 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>260.6670018406551</v>
+        <v>258.4235026489519</v>
       </c>
       <c r="D14" t="n">
-        <v>0.07667016983032227</v>
+        <v>0.1111607551574707</v>
       </c>
       <c r="E14" t="n">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="F14" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="G14" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="H14" t="n">
-        <v>413.1642344154005</v>
+        <v>397.0467708475732</v>
       </c>
       <c r="I14" t="n">
-        <v>0.2117581367492676</v>
+        <v>0.6337120532989502</v>
       </c>
       <c r="J14" t="n">
-        <v>73</v>
+        <v>94</v>
       </c>
       <c r="K14" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="L14" t="n">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="M14" t="n">
-        <v>1314.735974016285</v>
+        <v>1193.566968559136</v>
       </c>
       <c r="N14" t="n">
-        <v>1.471199035644531</v>
+        <v>1.405771970748901</v>
       </c>
       <c r="O14" t="n">
-        <v>396</v>
+        <v>577</v>
       </c>
       <c r="P14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>1087</v>
+        <v>1470</v>
       </c>
       <c r="R14" t="n">
-        <v>0.8017343352640123</v>
+        <v>0.7834863820327413</v>
       </c>
       <c r="S14" t="n">
-        <v>0.6857435693698584</v>
+        <v>0.6673443708593204</v>
       </c>
     </row>
     <row r="15">
@@ -1323,55 +1323,55 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>192.1215695400798</v>
+        <v>207.9436349887766</v>
       </c>
       <c r="D15" t="n">
-        <v>0.1137499809265137</v>
+        <v>0.1061501502990723</v>
       </c>
       <c r="E15" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F15" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G15" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H15" t="n">
-        <v>487.0275216777295</v>
+        <v>391.7370094163257</v>
       </c>
       <c r="I15" t="n">
-        <v>0.2181611061096191</v>
+        <v>0.7383689880371094</v>
       </c>
       <c r="J15" t="n">
-        <v>76</v>
+        <v>106</v>
       </c>
       <c r="K15" t="n">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="L15" t="n">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="M15" t="n">
-        <v>1352.954677802658</v>
+        <v>1190.768274814653</v>
       </c>
       <c r="N15" t="n">
-        <v>1.34666109085083</v>
+        <v>1.7187180519104</v>
       </c>
       <c r="O15" t="n">
-        <v>390</v>
+        <v>544</v>
       </c>
       <c r="P15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q15" t="n">
-        <v>1079</v>
+        <v>1451</v>
       </c>
       <c r="R15" t="n">
-        <v>0.8579985178423672</v>
+        <v>0.8253701921802177</v>
       </c>
       <c r="S15" t="n">
-        <v>0.6400267284128736</v>
+        <v>0.6710216272118091</v>
       </c>
     </row>
     <row r="16">
@@ -1384,55 +1384,55 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>219.6223835250067</v>
+        <v>222.3633408401805</v>
       </c>
       <c r="D16" t="n">
-        <v>0.06743025779724121</v>
+        <v>0.1080038547515869</v>
       </c>
       <c r="E16" t="n">
-        <v>88</v>
+        <v>67</v>
       </c>
       <c r="F16" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G16" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="H16" t="n">
-        <v>507.6491187052185</v>
+        <v>369.404685544578</v>
       </c>
       <c r="I16" t="n">
-        <v>0.1955492496490479</v>
+        <v>0.5288949012756348</v>
       </c>
       <c r="J16" t="n">
-        <v>98</v>
+        <v>85</v>
       </c>
       <c r="K16" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="L16" t="n">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="M16" t="n">
-        <v>1294.850734078759</v>
+        <v>1197.743766270911</v>
       </c>
       <c r="N16" t="n">
-        <v>1.435168981552124</v>
+        <v>1.486088037490845</v>
       </c>
       <c r="O16" t="n">
-        <v>383</v>
+        <v>556</v>
       </c>
       <c r="P16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q16" t="n">
-        <v>1016</v>
+        <v>1428</v>
       </c>
       <c r="R16" t="n">
-        <v>0.8303878758031054</v>
+        <v>0.8143481543364716</v>
       </c>
       <c r="S16" t="n">
-        <v>0.6079477693107282</v>
+        <v>0.6915828777847095</v>
       </c>
     </row>
     <row r="17">
@@ -1445,55 +1445,55 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>224.1694481173037</v>
+        <v>162.9618499721861</v>
       </c>
       <c r="D17" t="n">
-        <v>0.06314301490783691</v>
+        <v>0.1094999313354492</v>
       </c>
       <c r="E17" t="n">
-        <v>69</v>
+        <v>80</v>
       </c>
       <c r="F17" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="G17" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="H17" t="n">
-        <v>412.5793665354506</v>
+        <v>376.8787878591771</v>
       </c>
       <c r="I17" t="n">
-        <v>0.1423990726470947</v>
+        <v>0.5830399990081787</v>
       </c>
       <c r="J17" t="n">
-        <v>64</v>
+        <v>95</v>
       </c>
       <c r="K17" t="n">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="L17" t="n">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="M17" t="n">
-        <v>1311.895668811148</v>
+        <v>1205.813322089159</v>
       </c>
       <c r="N17" t="n">
-        <v>1.570755004882812</v>
+        <v>1.378974914550781</v>
       </c>
       <c r="O17" t="n">
-        <v>392</v>
+        <v>551</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q17" t="n">
-        <v>1016</v>
+        <v>1482</v>
       </c>
       <c r="R17" t="n">
-        <v>0.8291255520948184</v>
+        <v>0.8648531684076578</v>
       </c>
       <c r="S17" t="n">
-        <v>0.6855090108580555</v>
+        <v>0.6874484790015363</v>
       </c>
     </row>
     <row r="18">
@@ -1506,55 +1506,55 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>200.6883957578113</v>
+        <v>252.5293263651952</v>
       </c>
       <c r="D18" t="n">
-        <v>0.05972099304199219</v>
+        <v>0.09690594673156738</v>
       </c>
       <c r="E18" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F18" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G18" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H18" t="n">
-        <v>460.194130242934</v>
+        <v>391.7223510564938</v>
       </c>
       <c r="I18" t="n">
-        <v>0.1679129600524902</v>
+        <v>0.5178780555725098</v>
       </c>
       <c r="J18" t="n">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="K18" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="L18" t="n">
-        <v>92</v>
+        <v>78</v>
       </c>
       <c r="M18" t="n">
-        <v>1345.868550977987</v>
+        <v>1232.815108885544</v>
       </c>
       <c r="N18" t="n">
-        <v>2.279620170593262</v>
+        <v>1.466780185699463</v>
       </c>
       <c r="O18" t="n">
-        <v>392</v>
+        <v>565</v>
       </c>
       <c r="P18" t="n">
         <v>1</v>
       </c>
       <c r="Q18" t="n">
-        <v>1033</v>
+        <v>1473</v>
       </c>
       <c r="R18" t="n">
-        <v>0.8508855893749955</v>
+        <v>0.7951604222359995</v>
       </c>
       <c r="S18" t="n">
-        <v>0.6580690366020293</v>
+        <v>0.6822537716863253</v>
       </c>
     </row>
     <row r="19">
@@ -1567,55 +1567,55 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>246.5196652850749</v>
+        <v>219.6759946119212</v>
       </c>
       <c r="D19" t="n">
-        <v>0.05565118789672852</v>
+        <v>0.1272866725921631</v>
       </c>
       <c r="E19" t="n">
-        <v>63</v>
+        <v>77</v>
       </c>
       <c r="F19" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="G19" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H19" t="n">
-        <v>384.7869158456077</v>
+        <v>338.1353230064613</v>
       </c>
       <c r="I19" t="n">
-        <v>0.3347768783569336</v>
+        <v>0.6698729991912842</v>
       </c>
       <c r="J19" t="n">
-        <v>67</v>
+        <v>90</v>
       </c>
       <c r="K19" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="L19" t="n">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="M19" t="n">
-        <v>1284.764729539147</v>
+        <v>1185.078131758408</v>
       </c>
       <c r="N19" t="n">
-        <v>1.597488164901733</v>
+        <v>1.561012983322144</v>
       </c>
       <c r="O19" t="n">
-        <v>397</v>
+        <v>568</v>
       </c>
       <c r="P19" t="n">
         <v>1</v>
       </c>
       <c r="Q19" t="n">
-        <v>1081</v>
+        <v>1492</v>
       </c>
       <c r="R19" t="n">
-        <v>0.8081207713621599</v>
+        <v>0.8146316359023789</v>
       </c>
       <c r="S19" t="n">
-        <v>0.7005000939093081</v>
+        <v>0.7146725486320979</v>
       </c>
     </row>
     <row r="20">
@@ -1628,55 +1628,55 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>248.4061232942183</v>
+        <v>209.4538172660068</v>
       </c>
       <c r="D20" t="n">
-        <v>0.04944396018981934</v>
+        <v>0.1109049320220947</v>
       </c>
       <c r="E20" t="n">
-        <v>54</v>
+        <v>80</v>
       </c>
       <c r="F20" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="G20" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H20" t="n">
-        <v>519.9840626263589</v>
+        <v>368.4764602758498</v>
       </c>
       <c r="I20" t="n">
-        <v>0.1628389358520508</v>
+        <v>0.772507905960083</v>
       </c>
       <c r="J20" t="n">
-        <v>72</v>
+        <v>102</v>
       </c>
       <c r="K20" t="n">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="L20" t="n">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="M20" t="n">
-        <v>1307.399475972371</v>
+        <v>1222.905455819426</v>
       </c>
       <c r="N20" t="n">
-        <v>1.445517063140869</v>
+        <v>1.501938819885254</v>
       </c>
       <c r="O20" t="n">
-        <v>395</v>
+        <v>574</v>
       </c>
       <c r="P20" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Q20" t="n">
-        <v>1071</v>
+        <v>1525</v>
       </c>
       <c r="R20" t="n">
-        <v>0.8099998295398828</v>
+        <v>0.8287244395964698</v>
       </c>
       <c r="S20" t="n">
-        <v>0.602276066204154</v>
+        <v>0.6986876961564076</v>
       </c>
     </row>
     <row r="21">
@@ -1689,55 +1689,55 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>292.6617953377432</v>
+        <v>255.0114148683904</v>
       </c>
       <c r="D21" t="n">
-        <v>0.05940771102905273</v>
+        <v>0.08978009223937988</v>
       </c>
       <c r="E21" t="n">
-        <v>72</v>
+        <v>50</v>
       </c>
       <c r="F21" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G21" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H21" t="n">
-        <v>405.2407795815799</v>
+        <v>383.3050648530892</v>
       </c>
       <c r="I21" t="n">
-        <v>0.1492810249328613</v>
+        <v>0.5241239070892334</v>
       </c>
       <c r="J21" t="n">
-        <v>73</v>
+        <v>89</v>
       </c>
       <c r="K21" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="L21" t="n">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="M21" t="n">
-        <v>1328.147931534885</v>
+        <v>1176.699551584365</v>
       </c>
       <c r="N21" t="n">
-        <v>1.450638771057129</v>
+        <v>1.423141956329346</v>
       </c>
       <c r="O21" t="n">
-        <v>397</v>
+        <v>551</v>
       </c>
       <c r="P21" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Q21" t="n">
-        <v>1090</v>
+        <v>1438</v>
       </c>
       <c r="R21" t="n">
-        <v>0.7796466881520296</v>
+        <v>0.7832824746767084</v>
       </c>
       <c r="S21" t="n">
-        <v>0.6948827988511339</v>
+        <v>0.6742540911679715</v>
       </c>
     </row>
     <row r="22">
@@ -1750,55 +1750,55 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>194.7917806092164</v>
+        <v>198.1772313644063</v>
       </c>
       <c r="D22" t="n">
-        <v>0.04952597618103027</v>
+        <v>0.0967557430267334</v>
       </c>
       <c r="E22" t="n">
-        <v>57</v>
+        <v>70</v>
       </c>
       <c r="F22" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G22" t="n">
+        <v>5</v>
+      </c>
+      <c r="H22" t="n">
+        <v>342.6903115774451</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0.4193689823150635</v>
+      </c>
+      <c r="J22" t="n">
+        <v>80</v>
+      </c>
+      <c r="K22" t="n">
+        <v>12</v>
+      </c>
+      <c r="L22" t="n">
+        <v>72</v>
+      </c>
+      <c r="M22" t="n">
+        <v>1229.327374080444</v>
+      </c>
+      <c r="N22" t="n">
+        <v>1.591733932495117</v>
+      </c>
+      <c r="O22" t="n">
+        <v>558</v>
+      </c>
+      <c r="P22" t="n">
         <v>1</v>
       </c>
-      <c r="H22" t="n">
-        <v>457.74477141786</v>
-      </c>
-      <c r="I22" t="n">
-        <v>0.1548800468444824</v>
-      </c>
-      <c r="J22" t="n">
-        <v>67</v>
-      </c>
-      <c r="K22" t="n">
-        <v>26</v>
-      </c>
-      <c r="L22" t="n">
-        <v>90</v>
-      </c>
-      <c r="M22" t="n">
-        <v>1324.819841613343</v>
-      </c>
-      <c r="N22" t="n">
-        <v>1.894325017929077</v>
-      </c>
-      <c r="O22" t="n">
-        <v>389</v>
-      </c>
-      <c r="P22" t="n">
-        <v>3</v>
-      </c>
       <c r="Q22" t="n">
-        <v>1067</v>
+        <v>1440</v>
       </c>
       <c r="R22" t="n">
-        <v>0.8529673435657468</v>
+        <v>0.8387921431322181</v>
       </c>
       <c r="S22" t="n">
-        <v>0.6544852688344204</v>
+        <v>0.7212375492461618</v>
       </c>
     </row>
     <row r="23">
@@ -1811,55 +1811,55 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>219.9258533317122</v>
+        <v>178.0997967060643</v>
       </c>
       <c r="D23" t="n">
-        <v>0.07167911529541016</v>
+        <v>0.1526589393615723</v>
       </c>
       <c r="E23" t="n">
-        <v>64</v>
+        <v>88</v>
       </c>
       <c r="F23" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="G23" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H23" t="n">
-        <v>436.3225916591301</v>
+        <v>366.3070468131683</v>
       </c>
       <c r="I23" t="n">
-        <v>0.2918000221252441</v>
+        <v>0.6737937927246094</v>
       </c>
       <c r="J23" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="K23" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="L23" t="n">
-        <v>91</v>
+        <v>69</v>
       </c>
       <c r="M23" t="n">
-        <v>1283.288507894626</v>
+        <v>1220.044169033355</v>
       </c>
       <c r="N23" t="n">
-        <v>1.575126886367798</v>
+        <v>1.622098207473755</v>
       </c>
       <c r="O23" t="n">
-        <v>392</v>
+        <v>536</v>
       </c>
       <c r="P23" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q23" t="n">
-        <v>1083</v>
+        <v>1308</v>
       </c>
       <c r="R23" t="n">
-        <v>0.8286232191913536</v>
+        <v>0.8540218450884663</v>
       </c>
       <c r="S23" t="n">
-        <v>0.6599964941827738</v>
+        <v>0.6997591922402329</v>
       </c>
     </row>
     <row r="24">
@@ -1872,55 +1872,55 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>249.5164880972192</v>
+        <v>243.170388166996</v>
       </c>
       <c r="D24" t="n">
-        <v>0.04988217353820801</v>
+        <v>0.1954667568206787</v>
       </c>
       <c r="E24" t="n">
-        <v>60</v>
+        <v>88</v>
       </c>
       <c r="F24" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="G24" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="H24" t="n">
-        <v>437.7338277991063</v>
+        <v>394.2848586816898</v>
       </c>
       <c r="I24" t="n">
-        <v>0.1615080833435059</v>
+        <v>0.53078293800354</v>
       </c>
       <c r="J24" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="K24" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="L24" t="n">
-        <v>98</v>
+        <v>77</v>
       </c>
       <c r="M24" t="n">
-        <v>1317.473715476293</v>
+        <v>1202.123310716826</v>
       </c>
       <c r="N24" t="n">
-        <v>1.349697113037109</v>
+        <v>1.42135214805603</v>
       </c>
       <c r="O24" t="n">
-        <v>391</v>
+        <v>556</v>
       </c>
       <c r="P24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q24" t="n">
-        <v>1110</v>
+        <v>1402</v>
       </c>
       <c r="R24" t="n">
-        <v>0.810609892883507</v>
+        <v>0.7977159364608</v>
       </c>
       <c r="S24" t="n">
-        <v>0.667747581862871</v>
+        <v>0.6720096389724132</v>
       </c>
     </row>
     <row r="25">
@@ -1933,55 +1933,55 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>219.0549604705647</v>
+        <v>211.139469904686</v>
       </c>
       <c r="D25" t="n">
-        <v>0.04714608192443848</v>
+        <v>0.1145970821380615</v>
       </c>
       <c r="E25" t="n">
-        <v>59</v>
+        <v>76</v>
       </c>
       <c r="F25" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G25" t="n">
+        <v>9</v>
+      </c>
+      <c r="H25" t="n">
+        <v>365.133625599193</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.4084198474884033</v>
+      </c>
+      <c r="J25" t="n">
+        <v>71</v>
+      </c>
+      <c r="K25" t="n">
+        <v>17</v>
+      </c>
+      <c r="L25" t="n">
+        <v>67</v>
+      </c>
+      <c r="M25" t="n">
+        <v>1229.96800980894</v>
+      </c>
+      <c r="N25" t="n">
+        <v>1.44677209854126</v>
+      </c>
+      <c r="O25" t="n">
+        <v>533</v>
+      </c>
+      <c r="P25" t="n">
         <v>2</v>
       </c>
-      <c r="H25" t="n">
-        <v>445.8507411004219</v>
-      </c>
-      <c r="I25" t="n">
-        <v>0.1449530124664307</v>
-      </c>
-      <c r="J25" t="n">
-        <v>67</v>
-      </c>
-      <c r="K25" t="n">
-        <v>24</v>
-      </c>
-      <c r="L25" t="n">
-        <v>90</v>
-      </c>
-      <c r="M25" t="n">
-        <v>1343.436894661678</v>
-      </c>
-      <c r="N25" t="n">
-        <v>1.613457202911377</v>
-      </c>
-      <c r="O25" t="n">
-        <v>406</v>
-      </c>
-      <c r="P25" t="n">
-        <v>3</v>
-      </c>
       <c r="Q25" t="n">
-        <v>1122</v>
+        <v>1353</v>
       </c>
       <c r="R25" t="n">
-        <v>0.8369443616287388</v>
+        <v>0.8283374297373117</v>
       </c>
       <c r="S25" t="n">
-        <v>0.668126770321652</v>
+        <v>0.7031356728896454</v>
       </c>
     </row>
     <row r="26">
@@ -1994,55 +1994,55 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>295.7943307815479</v>
+        <v>281.4945375098412</v>
       </c>
       <c r="D26" t="n">
-        <v>0.05904984474182129</v>
+        <v>0.1014089584350586</v>
       </c>
       <c r="E26" t="n">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="F26" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="G26" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H26" t="n">
-        <v>422.6493288803179</v>
+        <v>355.7255183488852</v>
       </c>
       <c r="I26" t="n">
-        <v>0.1574068069458008</v>
+        <v>0.4536049365997314</v>
       </c>
       <c r="J26" t="n">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="K26" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L26" t="n">
-        <v>88</v>
+        <v>71</v>
       </c>
       <c r="M26" t="n">
-        <v>1319.808584581653</v>
+        <v>1188.79140106335</v>
       </c>
       <c r="N26" t="n">
-        <v>1.595078706741333</v>
+        <v>1.76846718788147</v>
       </c>
       <c r="O26" t="n">
-        <v>382</v>
+        <v>556</v>
       </c>
       <c r="P26" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q26" t="n">
-        <v>1002</v>
+        <v>1446</v>
       </c>
       <c r="R26" t="n">
-        <v>0.7758808858821694</v>
+        <v>0.763209477072218</v>
       </c>
       <c r="S26" t="n">
-        <v>0.679764676622188</v>
+        <v>0.7007670832488392</v>
       </c>
     </row>
     <row r="27">
@@ -2055,55 +2055,55 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>240.6732401765218</v>
+        <v>225.110240380804</v>
       </c>
       <c r="D27" t="n">
-        <v>0.06173396110534668</v>
+        <v>0.129641056060791</v>
       </c>
       <c r="E27" t="n">
-        <v>61</v>
+        <v>74</v>
       </c>
       <c r="F27" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G27" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="H27" t="n">
-        <v>464.9734636503963</v>
+        <v>379.0765273166276</v>
       </c>
       <c r="I27" t="n">
-        <v>0.2217233180999756</v>
+        <v>0.716655969619751</v>
       </c>
       <c r="J27" t="n">
-        <v>78</v>
+        <v>105</v>
       </c>
       <c r="K27" t="n">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="L27" t="n">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="M27" t="n">
-        <v>1270.637783299976</v>
+        <v>1200.660207237661</v>
       </c>
       <c r="N27" t="n">
-        <v>1.554635047912598</v>
+        <v>1.510397911071777</v>
       </c>
       <c r="O27" t="n">
-        <v>388</v>
+        <v>550</v>
       </c>
       <c r="P27" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q27" t="n">
-        <v>1039</v>
+        <v>1378</v>
       </c>
       <c r="R27" t="n">
-        <v>0.8105886324649745</v>
+        <v>0.8125112841886287</v>
       </c>
       <c r="S27" t="n">
-        <v>0.6340629329919556</v>
+        <v>0.684276596299662</v>
       </c>
     </row>
     <row r="28">
@@ -2116,55 +2116,55 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>229.7049189542186</v>
+        <v>257.1152125947239</v>
       </c>
       <c r="D28" t="n">
-        <v>0.06202912330627441</v>
+        <v>0.09787988662719727</v>
       </c>
       <c r="E28" t="n">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="F28" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G28" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H28" t="n">
-        <v>466.4988977562555</v>
+        <v>376.3655082952552</v>
       </c>
       <c r="I28" t="n">
-        <v>0.2131707668304443</v>
+        <v>0.4778509140014648</v>
       </c>
       <c r="J28" t="n">
         <v>85</v>
       </c>
       <c r="K28" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="L28" t="n">
-        <v>102</v>
+        <v>78</v>
       </c>
       <c r="M28" t="n">
-        <v>1288.961301848084</v>
+        <v>1197.963225009772</v>
       </c>
       <c r="N28" t="n">
-        <v>1.370229959487915</v>
+        <v>1.438938140869141</v>
       </c>
       <c r="O28" t="n">
-        <v>403</v>
+        <v>569</v>
       </c>
       <c r="P28" t="n">
         <v>2</v>
       </c>
       <c r="Q28" t="n">
-        <v>1082</v>
+        <v>1451</v>
       </c>
       <c r="R28" t="n">
-        <v>0.821790678568183</v>
+        <v>0.7853730338069213</v>
       </c>
       <c r="S28" t="n">
-        <v>0.6380815334894852</v>
+        <v>0.685828829768806</v>
       </c>
     </row>
     <row r="29">
@@ -2177,55 +2177,55 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>235.9913497262016</v>
+        <v>235.042044505378</v>
       </c>
       <c r="D29" t="n">
-        <v>0.06836771965026855</v>
+        <v>0.1279349327087402</v>
       </c>
       <c r="E29" t="n">
-        <v>57</v>
+        <v>88</v>
       </c>
       <c r="F29" t="n">
+        <v>8</v>
+      </c>
+      <c r="G29" t="n">
+        <v>11</v>
+      </c>
+      <c r="H29" t="n">
+        <v>428.0831817266134</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0.4973688125610352</v>
+      </c>
+      <c r="J29" t="n">
+        <v>83</v>
+      </c>
+      <c r="K29" t="n">
         <v>17</v>
       </c>
-      <c r="G29" t="n">
-        <v>4</v>
-      </c>
-      <c r="H29" t="n">
-        <v>476.6791829019649</v>
-      </c>
-      <c r="I29" t="n">
-        <v>0.1754188537597656</v>
-      </c>
-      <c r="J29" t="n">
-        <v>71</v>
-      </c>
-      <c r="K29" t="n">
-        <v>22</v>
-      </c>
       <c r="L29" t="n">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="M29" t="n">
-        <v>1332.076028684385</v>
+        <v>1208.719510310128</v>
       </c>
       <c r="N29" t="n">
-        <v>1.428467988967896</v>
+        <v>1.357059240341187</v>
       </c>
       <c r="O29" t="n">
-        <v>385</v>
+        <v>576</v>
       </c>
       <c r="P29" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q29" t="n">
-        <v>1047</v>
+        <v>1448</v>
       </c>
       <c r="R29" t="n">
-        <v>0.822839429098295</v>
+        <v>0.8055445928517594</v>
       </c>
       <c r="S29" t="n">
-        <v>0.6421531709622059</v>
+        <v>0.6458374518859403</v>
       </c>
     </row>
     <row r="30">
@@ -2238,55 +2238,55 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>244.197591904272</v>
+        <v>205.9843030513724</v>
       </c>
       <c r="D30" t="n">
-        <v>0.05946588516235352</v>
+        <v>0.1014881134033203</v>
       </c>
       <c r="E30" t="n">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="F30" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="G30" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H30" t="n">
-        <v>541.8626337395824</v>
+        <v>387.312644878035</v>
       </c>
       <c r="I30" t="n">
-        <v>0.1986172199249268</v>
+        <v>0.7888257503509521</v>
       </c>
       <c r="J30" t="n">
-        <v>81</v>
+        <v>95</v>
       </c>
       <c r="K30" t="n">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="L30" t="n">
-        <v>106</v>
+        <v>87</v>
       </c>
       <c r="M30" t="n">
-        <v>1350.558695709065</v>
+        <v>1211.993925437751</v>
       </c>
       <c r="N30" t="n">
-        <v>1.450552701950073</v>
+        <v>1.500679969787598</v>
       </c>
       <c r="O30" t="n">
-        <v>380</v>
+        <v>546</v>
       </c>
       <c r="P30" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Q30" t="n">
-        <v>1017</v>
+        <v>1369</v>
       </c>
       <c r="R30" t="n">
-        <v>0.8191877238063582</v>
+        <v>0.8300451027615716</v>
       </c>
       <c r="S30" t="n">
-        <v>0.5987863130560972</v>
+        <v>0.6804335098147093</v>
       </c>
     </row>
     <row r="31">
@@ -2299,55 +2299,55 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>246.9711713231257</v>
+        <v>217.5324847804119</v>
       </c>
       <c r="D31" t="n">
-        <v>0.111037015914917</v>
+        <v>0.09263014793395996</v>
       </c>
       <c r="E31" t="n">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="F31" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="G31" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H31" t="n">
-        <v>525.7408045664454</v>
+        <v>426.0765010735613</v>
       </c>
       <c r="I31" t="n">
-        <v>0.3775351047515869</v>
+        <v>0.8987739086151123</v>
       </c>
       <c r="J31" t="n">
-        <v>71</v>
+        <v>100</v>
       </c>
       <c r="K31" t="n">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="L31" t="n">
         <v>94</v>
       </c>
       <c r="M31" t="n">
-        <v>1294.287187402866</v>
+        <v>1193.071276785229</v>
       </c>
       <c r="N31" t="n">
-        <v>2.72478985786438</v>
+        <v>1.484001159667969</v>
       </c>
       <c r="O31" t="n">
-        <v>408</v>
+        <v>568</v>
       </c>
       <c r="P31" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q31" t="n">
-        <v>1147</v>
+        <v>1480</v>
       </c>
       <c r="R31" t="n">
-        <v>0.8091836388964792</v>
+        <v>0.8176701685698439</v>
       </c>
       <c r="S31" t="n">
-        <v>0.5937989576939227</v>
+        <v>0.6428742277480363</v>
       </c>
     </row>
   </sheetData>
